--- a/docs/강민준_분식집키오스크_작업일지.xlsx
+++ b/docs/강민준_분식집키오스크_작업일지.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>메뉴·옵션 이미지의 업로드·교체·삭제 처리와 이미지 URL 반환 방식을 구현함. API 응답을 공통 ApiResponse 형식으로 감싸도록 적용함.</t>
+          <t>메뉴·옵션 이미지의 업로드·교체·삭제 처리와 이미지 URL 반환 방식을 구현함. 이미지를 교체할 때 기존 업로드 파일도 함께 삭제되도록 정리하고, API 응답을 공통 ApiResponse 형식으로 감싸도록 적용함.</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>JWT 관리자 로그인을 프론트·백엔드에 연결하고 Spring Security 필터와 권한 설정을 구성함. 인증 실패 401과 권한 부족 403 응답 형식을 통일하고 관련 코드를 정리함.</t>
+          <t>JWT 관리자 로그인을 프론트·백엔드에 연결하고 Spring Security 필터와 권한 설정을 구성함. 인증 실패 401과 권한 부족 403 응답 형식을 통일하고, 관리자 주문 취소 프론트·백엔드 연동과 관련 코드를 정리함.</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>관리자 매출 대시보드에 매출 추이·인기 메뉴·결제 수단 차트를 구성함. 메뉴 영문 정보와 판매 중단·재개 처리를 보완하고 매출 API 응답을 화면 요구사항에 맞게 현행화함.</t>
+          <t>관리자 매출 대시보드에 매출 추이·인기 메뉴·결제 수단 차트를 구성하고 매출 요약·인기 메뉴·매출 이력 API를 현행화함. 메뉴 영문 정보와 판매 중단·재개 처리를 보완하고 REST API 명세 30건을 최신 구현에 맞게 정리함.</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>주문관리 화면에서 주문별 메뉴·옵션 상세 정보를 조회하도록 구현함. 백엔드 자동 테스트를 보강하고 JWT 비밀값을 환경변수로 분리했으며 README 실행·설정 내용을 정리함.</t>
+          <t>주문관리 화면에서 주문별 메뉴·옵션 상세 정보를 조회하도록 구현함. 관리자 백엔드 테스트 파일 3개·총 14개 테스트를 확인하고 JWT 비밀값을 환경변수로 분리했으며 README 실행·설정 내용을 정리함.</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>관리자 메뉴관리 화면을 폼·목록·세트 구성 컴포넌트로 분리하여 리팩터링함. 메뉴 유형과 세트 추가금액 데이터를 분리하고 완료 주문의 매출 반영, 관리자 로그인 5회 제한을 적용함.</t>
+          <t>관리자 메뉴관리 화면을 폼·목록·세트 구성 컴포넌트로 분리하여 리팩터링함. 메뉴 유형과 세트 추가금액 데이터를 분리하고 완료 주문의 매출 반영, 관리자 로그인 5회 제한을 적용함. 매출 결과를 CSV·Excel로 내려받는 기능과 결제수단별 통계를 추가함.</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>세트 메뉴의 맛·구성 선택 UI와 구성 전용 메뉴 필터를 적용함. 신규 주문 배지, 일정 시간 지연 주문 경고, 어느 관리자 화면에서든 표시되는 전역 주문 알림 토스트와 소리를 구현하고 테스트함.</t>
+          <t>세트 메뉴의 맛·구성 선택 UI와 is_component_only 기반 구성 전용 메뉴 필터를 적용함. 주문을 5초마다 갱신하고 접수 후 10분이 지난 주문을 지연 표시하도록 구현했으며, 어느 관리자 화면에서든 표시되는 신규 주문 배지·전역 토스트·알림음을 테스트함.</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>관리자 최신 프론트 자동 테스트를 실행하고 API 주소를 localhost로 고정하던 메뉴·옵션 API 테스트를 환경변수 기준으로 보정하여 65건 전체 통과를 확인함. 실제 태블릿용 관리자 테스트 체크리스트 20개 항목을 작성하고, 관리자 프로덕션 빌드를 생성하여 배포 파일 생성 성공을 확인함. 프론트·백엔드 구조와 기술 버전을 재점검하고 프로젝트 구조 문서를 보강함.</t>
+          <t>관리자 최신 프론트 자동 테스트를 실행하고 API 주소를 localhost로 고정하던 메뉴·옵션 API 테스트를 환경변수 기준으로 보정하여 65건 전체 통과를 확인함. 실제 태블릿용 관리자 테스트 체크리스트 20개 항목을 작성하고 관리자 프로덕션 빌드 성공을 검증함. 프론트·백엔드 구조와 기술 버전을 재점검해 프로젝트 구조 문서를 보강하고 개인·팀 전체 작업일지를 생성함. 발표자료 25개 슬라이드와 관리자·고객 프론트 전체 파일을 스캔하여 누락된 관리자 기능, 실제 버전, 테스트·빌드 결과 및 고객 build 원복 상태를 확인함.</t>
         </is>
       </c>
     </row>

--- a/docs/강민준_분식집키오스크_작업일지.xlsx
+++ b/docs/강민준_분식집키오스크_작업일지.xlsx
@@ -119,7 +119,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>담당자: 강민준 | 기간: 2026-07-13 ~ 2026-08-10</t>
+          <t>담당자: 강민준 | 기간: 2026-07-13 ~ 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -143,7 +143,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>22일</t>
+          <t>23일</t>
         </is>
       </c>
     </row>
@@ -634,11 +634,26 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="6">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>관리자 프론트 자동 테스트 19개 파일에 테스트 목적과 검증 범위를 설명하는 주석을 추가하여 테스트 코드의 가독성과 유지보수성을 높임. 고객 키오스크 Playwright E2E 실행 환경을 점검하고 매장식사·포장·옵션·세트 메뉴의 핵심 주문 흐름 4건이 모두 통과하는 것을 확인했으며, VS Code의 @ts-check 커스텀 fixture 타입 경고가 실제 테스트 실패와 무관함을 분석함. 프로젝트 결과 보고서와 발표 PPT의 내용 구성·검토 및 작성 작업에 협력함.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <autoFilter ref="A3:C25"/>
+  <autoFilter ref="A3:C26"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
 </worksheet>
 </file>

--- a/docs/강민준_분식집키오스크_작업일지.xlsx
+++ b/docs/강민준_분식집키오스크_작업일지.xlsx
@@ -119,7 +119,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>담당자: 강민준 | 기간: 2026-07-13 ~ 2026-08-13</t>
+          <t>담당자: 강민준 | 기간: 2026-07-13 ~ 2026-08-14</t>
         </is>
       </c>
     </row>
@@ -143,7 +143,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>23일</t>
+          <t>24일</t>
         </is>
       </c>
     </row>
@@ -155,7 +155,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>27건 (모두 DONE)</t>
+          <t>28건 (모두 DONE)</t>
         </is>
       </c>
     </row>
@@ -649,11 +649,26 @@
         </is>
       </c>
     </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="6">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>관리자 키오스크에 Playwright E2E를 구성하여 비로그인 접근 차단, 정상 로그인, 메뉴 등록·수정·판매중단, 주문 상세 및 상태 변경 흐름을 검증함. 주문관리 화면에 체크박스 기반 다중 선택을 추가하고 동일 상태 주문의 일괄 조리 시작·완료와 접수·조리중 혼합 주문의 다중 취소를 구현함. 백엔드에 다중 상태 변경·다중 취소 API와 전체 사전 검증, Toss·카카오 주문별 전액 환불 및 관리자 이력 저장을 적용함. 관리자 프론트 테스트 69건, E2E 6건, 프로덕션 빌드와 백엔드 전체 테스트 통과를 확인함. 프론트·백엔드 전체 구조와 기술 버전을 재검수하여 시스템 구조 이미지를 수정하고 DevProject Hub에 요구사항 PLAN-ORDER-028, API 명세, QA, 시나리오와 WBS 완료 기록을 최신화함.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <autoFilter ref="A3:C26"/>
+  <autoFilter ref="A3:C27"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
 </worksheet>
 </file>

--- a/docs/강민준_분식집키오스크_작업일지.xlsx
+++ b/docs/강민준_분식집키오스크_작업일지.xlsx
@@ -119,7 +119,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>담당자: 강민준 | 기간: 2026-07-13 ~ 2026-08-14</t>
+          <t>담당자: 강민준 | 기간: 2026-07-13 ~ 2026-08-18</t>
         </is>
       </c>
     </row>
@@ -143,7 +143,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>24일</t>
+          <t>25일</t>
         </is>
       </c>
     </row>
@@ -155,7 +155,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>28건 (모두 DONE)</t>
+          <t>37건 (모두 DONE)</t>
         </is>
       </c>
     </row>
@@ -203,7 +203,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JWT 로그인, 보호 라우팅, Spring Security, 401/403 공통 응답, 환경변수 분리</t>
+          <t>JWT 로그인, 보호 라우팅, 401/403 공통 응답, 1시간 무동작 자동 로그아웃 사전 경고, 환경변수 분리</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>프론트·백엔드 자동 테스트, API 명세 현행화, README와 .env.example 정비</t>
+          <t>프론트·백엔드 자동 테스트, 조회 실패·재시도 예외 처리, API 명세와 DevProject Hub 현행화</t>
         </is>
       </c>
     </row>
@@ -664,11 +664,26 @@
         </is>
       </c>
     </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="6">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>기업 실무자 피드백 PDF를 검토하고 관리자 프론트 개선 항목을 구현함. 관리자 변경 이력에 처리자·처리시간과 로딩·빈 목록·오류 재시도를 추가하고, 메뉴·옵션 목록의 검색·카테고리·판매상태 필터 UI를 정리함. 주문 상태를 접수·조리중·완료·취소 색상 배지로 구분하고 상태 변경·취소 성공 및 실패 결과 메시지를 적용함. 관리자 무동작 59분에 사전 경고를 표시하고 60분에 자동 로그아웃하도록 개선했으며, 관리자 메인의 메뉴·옵션·주문 조회 실패를 항목별로 다시 시도할 수 있게 구현함. 관련 자동 테스트와 프로덕션 빌드를 통과시키고 DevProject Hub에 요구사항 5건, WBS 5건, 테스트 5건과 관리자 화면 설계 3건을 최신화함.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <autoFilter ref="A3:C27"/>
+  <autoFilter ref="A3:C28"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
 </worksheet>
 </file>

--- a/docs/강민준_분식집키오스크_작업일지.xlsx
+++ b/docs/강민준_분식집키오스크_작업일지.xlsx
@@ -119,7 +119,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>담당자: 강민준 | 기간: 2026-07-13 ~ 2026-08-18</t>
+          <t>담당자: 강민준 | 기간: 2026-07-13 ~ 2026-08-19</t>
         </is>
       </c>
     </row>
@@ -143,7 +143,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>25일</t>
+          <t>26일</t>
         </is>
       </c>
     </row>
@@ -679,11 +679,26 @@
         </is>
       </c>
     </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="6">
+        <v>26</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>관리자 주문관리에서 한국시간을 기준으로 일·주·월 단위의 주문을 조회할 수 있도록 기간 선택 필터를 구현하고 관련 자동 테스트 16건을 통과시킴. WSL2 Ubuntu에서 FreeRTOS POSIX 기반 BunShik_RTOS를 구축하고 관리자·고객 코드를 단일 프로젝트 구조로 통합함. 관리자 JWT 자동 로그인, 주문 목록·상세 조회, 상태 변경·취소, 10초 주기 주문 감시, 지연 주문 감지, 네트워크 재시도와 날짜별 로그를 구현했으며, 고객 연결·인쇄 감시·인쇄 Worker Task 및 Mutex·Semaphore·Task Notification 기반 동기화를 구성함. Windows에서 실행 중인 Spring Boot 백엔드와 연결하여 실제 주문 111건 동기화를 검증하고, Windows 호스트 주소 탐색과 CMake 재구성·빌드·실행을 자동화한 Makefile을 추가했으며 RTOS 자동 테스트 4건을 모두 통과시킴. 새 데이터베이스의 print_jobs 테이블과 영수증·주문표 인쇄 작업 API 구조를 확인하고, 대기 작업 조회 API의 HTTP 500 오류를 발견하여 미완료 점검 항목으로 기록함.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <autoFilter ref="A3:C28"/>
+  <autoFilter ref="A3:C29"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
 </worksheet>
 </file>

--- a/docs/강민준_분식집키오스크_작업일지.xlsx
+++ b/docs/강민준_분식집키오스크_작업일지.xlsx
@@ -119,7 +119,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>담당자: 강민준 | 기간: 2026-07-13 ~ 2026-08-19</t>
+          <t>담당자: 강민준 | 기간: 2026-07-13 ~ 2026-08-20</t>
         </is>
       </c>
     </row>
@@ -143,7 +143,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>26일</t>
+          <t>27일</t>
         </is>
       </c>
     </row>
@@ -155,7 +155,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>37건 (모두 DONE)</t>
+          <t>38건 (모두 DONE)</t>
         </is>
       </c>
     </row>
@@ -694,11 +694,26 @@
         </is>
       </c>
     </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="6">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>BunShik_RTOS Git 기록에서 관리자 기능 커밋 dc5c2ef와 관리자 감시 중복 오류 수정 커밋 04026f0을 확인함. admin_catalog_monitor 모듈을 추가하여 메뉴·옵션의 등록, 이름, 가격, 품절 및 판매 상태 변경을 주기적으로 감지하고 이벤트와 날짜별 로그로 기록하도록 구현함. 관리자 JWT 자동 로그인 이후 주문 감시와 카탈로그 감시가 함께 동작하도록 admin_service와 backend_client의 응답 파서를 보강하고, 네트워크 장애 재시도와 JWT 만료 시 자동 재로그인 흐름 및 중복 알림 방지를 정리함. backend_parser_test를 통과시키고 RTOS 회귀 테스트로 관리자 기능의 정상 동작을 확인했으며, DevProject Hub에 관리자 RTOS 요구사항 PLAN-SYS-026, WBS-083 및 테스트 TC-083을 최신화함. 박유진 담당 고객 키오스크·영수증·프린터 작업은 강민준 일지에서 제외함.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <autoFilter ref="A3:C29"/>
+  <autoFilter ref="A3:C30"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
